--- a/leads/leads.xlsx
+++ b/leads/leads.xlsx
@@ -431,11 +431,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Het Soni</t>
+          <t>Rajesh Gajjar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9327983260</v>
+        <v>9427047705</v>
       </c>
     </row>
   </sheetData>

--- a/leads/leads.xlsx
+++ b/leads/leads.xlsx
@@ -435,7 +435,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9427047705</v>
+        <v>919427047705</v>
       </c>
     </row>
   </sheetData>

--- a/leads/leads.xlsx
+++ b/leads/leads.xlsx
@@ -431,11 +431,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Rajesh Gajjar</t>
+          <t>Het Soni</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>919427047705</v>
+        <v>919327983260</v>
       </c>
     </row>
   </sheetData>

--- a/leads/leads.xlsx
+++ b/leads/leads.xlsx
@@ -419,12 +419,12 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>name</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Mobile Number</t>
+          <t>mobile number</t>
         </is>
       </c>
     </row>
